--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233600</v>
+        <v>121233606</v>
       </c>
       <c r="B2" t="n">
-        <v>98092</v>
+        <v>99092</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>222467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233592</v>
+        <v>121233604</v>
       </c>
       <c r="B3" t="n">
-        <v>98073</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233604</v>
+        <v>121233593</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>105171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121233606</v>
+        <v>121233592</v>
       </c>
       <c r="B5" t="n">
-        <v>99082</v>
+        <v>98083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222467</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233591</v>
+        <v>121233600</v>
       </c>
       <c r="B6" t="n">
-        <v>97989</v>
+        <v>98102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233593</v>
+        <v>121233583</v>
       </c>
       <c r="B7" t="n">
-        <v>105161</v>
+        <v>99799</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>1256</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233583</v>
+        <v>121233591</v>
       </c>
       <c r="B8" t="n">
-        <v>99789</v>
+        <v>97999</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1256</v>
+        <v>223591</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233606</v>
+        <v>121233599</v>
       </c>
       <c r="B2" t="n">
-        <v>99092</v>
+        <v>105171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222467</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233604</v>
+        <v>121233583</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>99799</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>1256</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233593</v>
+        <v>121233606</v>
       </c>
       <c r="B4" t="n">
-        <v>105171</v>
+        <v>99092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>222467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121233592</v>
+        <v>121233604</v>
       </c>
       <c r="B5" t="n">
-        <v>98083</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233583</v>
+        <v>121233591</v>
       </c>
       <c r="B7" t="n">
-        <v>99799</v>
+        <v>97999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1256</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233591</v>
+        <v>121233592</v>
       </c>
       <c r="B8" t="n">
-        <v>97999</v>
+        <v>98083</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233599</v>
+        <v>121233583</v>
       </c>
       <c r="B2" t="n">
-        <v>105171</v>
+        <v>99812</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>1256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233583</v>
+        <v>121233599</v>
       </c>
       <c r="B3" t="n">
-        <v>99799</v>
+        <v>105184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1256</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233606</v>
+        <v>121233591</v>
       </c>
       <c r="B4" t="n">
-        <v>99092</v>
+        <v>98012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222467</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>121233604</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233600</v>
+        <v>121233592</v>
       </c>
       <c r="B6" t="n">
-        <v>98102</v>
+        <v>98096</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233591</v>
+        <v>121233606</v>
       </c>
       <c r="B7" t="n">
-        <v>97999</v>
+        <v>99105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>222467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233592</v>
+        <v>121233600</v>
       </c>
       <c r="B8" t="n">
-        <v>98083</v>
+        <v>98115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233583</v>
+        <v>121233600</v>
       </c>
       <c r="B2" t="n">
-        <v>99812</v>
+        <v>98116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1256</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233599</v>
+        <v>121233592</v>
       </c>
       <c r="B3" t="n">
-        <v>105184</v>
+        <v>98097</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>121233591</v>
       </c>
       <c r="B4" t="n">
-        <v>98012</v>
+        <v>98013</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>121233604</v>
       </c>
       <c r="B5" t="n">
-        <v>98117</v>
+        <v>98118</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233592</v>
+        <v>121233599</v>
       </c>
       <c r="B6" t="n">
-        <v>98096</v>
+        <v>105185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233606</v>
+        <v>121233583</v>
       </c>
       <c r="B7" t="n">
-        <v>99105</v>
+        <v>99813</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222467</v>
+        <v>1256</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233600</v>
+        <v>121233606</v>
       </c>
       <c r="B8" t="n">
-        <v>98115</v>
+        <v>99106</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>222467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233600</v>
+        <v>121233591</v>
       </c>
       <c r="B2" t="n">
-        <v>98116</v>
+        <v>98016</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233592</v>
+        <v>121233600</v>
       </c>
       <c r="B3" t="n">
-        <v>98097</v>
+        <v>98119</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233591</v>
+        <v>121233592</v>
       </c>
       <c r="B4" t="n">
-        <v>98013</v>
+        <v>98100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121233604</v>
+        <v>121233599</v>
       </c>
       <c r="B5" t="n">
-        <v>98118</v>
+        <v>105188</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233599</v>
+        <v>121233606</v>
       </c>
       <c r="B6" t="n">
-        <v>105185</v>
+        <v>99109</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>222467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233583</v>
+        <v>121233604</v>
       </c>
       <c r="B7" t="n">
-        <v>99813</v>
+        <v>98121</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1256</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233606</v>
+        <v>121233583</v>
       </c>
       <c r="B8" t="n">
-        <v>99106</v>
+        <v>99816</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222467</v>
+        <v>1256</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233591</v>
+        <v>121233599</v>
       </c>
       <c r="B2" t="n">
-        <v>98016</v>
+        <v>105188</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233600</v>
+        <v>121233583</v>
       </c>
       <c r="B3" t="n">
-        <v>98119</v>
+        <v>99816</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1256</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233592</v>
+        <v>121233604</v>
       </c>
       <c r="B4" t="n">
-        <v>98100</v>
+        <v>98121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121233599</v>
+        <v>121233600</v>
       </c>
       <c r="B5" t="n">
-        <v>105188</v>
+        <v>98119</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233606</v>
+        <v>121233591</v>
       </c>
       <c r="B6" t="n">
-        <v>99109</v>
+        <v>98016</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222467</v>
+        <v>223591</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233604</v>
+        <v>121233606</v>
       </c>
       <c r="B7" t="n">
-        <v>98121</v>
+        <v>99109</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>222467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233583</v>
+        <v>121233592</v>
       </c>
       <c r="B8" t="n">
-        <v>99816</v>
+        <v>98100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1256</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121233599</v>
       </c>
       <c r="B2" t="n">
-        <v>105188</v>
+        <v>105194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233583</v>
+        <v>121233606</v>
       </c>
       <c r="B3" t="n">
-        <v>99816</v>
+        <v>99115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1256</v>
+        <v>222467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233604</v>
+        <v>121233591</v>
       </c>
       <c r="B4" t="n">
-        <v>98121</v>
+        <v>98022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121233600</v>
+        <v>121233583</v>
       </c>
       <c r="B5" t="n">
-        <v>98119</v>
+        <v>99822</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>1256</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233591</v>
+        <v>121233592</v>
       </c>
       <c r="B6" t="n">
-        <v>98016</v>
+        <v>98106</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233606</v>
+        <v>121233600</v>
       </c>
       <c r="B7" t="n">
-        <v>99109</v>
+        <v>98125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222467</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233592</v>
+        <v>121233604</v>
       </c>
       <c r="B8" t="n">
-        <v>98100</v>
+        <v>98127</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233599</v>
+        <v>121233604</v>
       </c>
       <c r="B2" t="n">
-        <v>105194</v>
+        <v>98128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233606</v>
+        <v>121233583</v>
       </c>
       <c r="B3" t="n">
-        <v>99115</v>
+        <v>99823</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222467</v>
+        <v>1256</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233591</v>
+        <v>121233592</v>
       </c>
       <c r="B4" t="n">
-        <v>98022</v>
+        <v>98107</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121233583</v>
+        <v>121233606</v>
       </c>
       <c r="B5" t="n">
-        <v>99822</v>
+        <v>99116</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1256</v>
+        <v>222467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233592</v>
+        <v>121233599</v>
       </c>
       <c r="B6" t="n">
-        <v>98106</v>
+        <v>105195</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233600</v>
+        <v>121233591</v>
       </c>
       <c r="B7" t="n">
-        <v>98125</v>
+        <v>98023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233604</v>
+        <v>121233600</v>
       </c>
       <c r="B8" t="n">
-        <v>98127</v>
+        <v>98126</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233604</v>
+        <v>121233583</v>
       </c>
       <c r="B2" t="n">
-        <v>98128</v>
+        <v>99823</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>1256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233583</v>
+        <v>121233592</v>
       </c>
       <c r="B3" t="n">
-        <v>99823</v>
+        <v>98107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1256</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233592</v>
+        <v>121233593</v>
       </c>
       <c r="B4" t="n">
-        <v>98107</v>
+        <v>105195</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233599</v>
+        <v>121233604</v>
       </c>
       <c r="B6" t="n">
-        <v>105195</v>
+        <v>98128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233583</v>
+        <v>121233592</v>
       </c>
       <c r="B2" t="n">
-        <v>99823</v>
+        <v>98107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1256</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233592</v>
+        <v>121233593</v>
       </c>
       <c r="B3" t="n">
-        <v>98107</v>
+        <v>105195</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233593</v>
+        <v>121233583</v>
       </c>
       <c r="B4" t="n">
-        <v>105195</v>
+        <v>99823</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>1256</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121233606</v>
+        <v>121233600</v>
       </c>
       <c r="B5" t="n">
-        <v>99116</v>
+        <v>98126</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222467</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233604</v>
+        <v>121233591</v>
       </c>
       <c r="B6" t="n">
-        <v>98128</v>
+        <v>98023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233591</v>
+        <v>121233604</v>
       </c>
       <c r="B7" t="n">
-        <v>98023</v>
+        <v>98128</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233600</v>
+        <v>121233606</v>
       </c>
       <c r="B8" t="n">
-        <v>98126</v>
+        <v>99116</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>222467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 34207-2020 artfynd.xlsx
+++ b/artfynd/A 34207-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121233592</v>
+        <v>121233604</v>
       </c>
       <c r="B2" t="n">
-        <v>98107</v>
+        <v>98128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121233593</v>
+        <v>121233591</v>
       </c>
       <c r="B3" t="n">
-        <v>105195</v>
+        <v>98023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121233583</v>
+        <v>121233592</v>
       </c>
       <c r="B4" t="n">
-        <v>99823</v>
+        <v>98107</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1256</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121233591</v>
+        <v>121233606</v>
       </c>
       <c r="B6" t="n">
-        <v>98023</v>
+        <v>99116</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>222467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Surdrag</t>
+          <t>Rikmyr, sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121233604</v>
+        <v>121233599</v>
       </c>
       <c r="B7" t="n">
-        <v>98128</v>
+        <v>105195</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121233606</v>
+        <v>121233583</v>
       </c>
       <c r="B8" t="n">
-        <v>99116</v>
+        <v>99823</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222467</v>
+        <v>1256</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikmyr, sumpskog</t>
+          <t>Surdrag</t>
         </is>
       </c>
       <c r="AD8" t="b">
